--- a/quant/tests/testthat/testdata/MRMhub_TestData_MHQuant_S1P_metadata_tables.xlsx
+++ b/quant/tests/testthat/testdata/MRMhub_TestData_MHQuant_S1P_metadata_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsibjb/Documents/Code/midar/tests/testthat/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lsibjb/Documents/Code/MRMhub/quant/tests/testthat/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9D0A5B-3AC6-2B47-8BB3-8CFF991FEDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42963ECC-275B-B540-AADF-3F18FAE6BEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="5180" windowWidth="38120" windowHeight="22160" activeTab="1" xr2:uid="{7A04E2C8-868F-5640-98CB-88D372530A12}"/>
+    <workbookView xWindow="8380" yWindow="5180" windowWidth="51400" windowHeight="22160" activeTab="15" xr2:uid="{7A04E2C8-868F-5640-98CB-88D372530A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Analyses" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,11 @@
     <sheet name="Features_missing_quan" sheetId="12" r:id="rId12"/>
     <sheet name="Features_inval_interf" sheetId="13" r:id="rId13"/>
     <sheet name="Features_miss_interf" sheetId="14" r:id="rId14"/>
+    <sheet name="Features_rfzero" sheetId="15" r:id="rId15"/>
+    <sheet name="Features_intefzero" sheetId="16" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId17"/>
   </externalReferences>
   <definedNames>
     <definedName name="SampleAmountUnit" localSheetId="5">[1]!Table2[Sample_Amount_Unit]</definedName>
@@ -71,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="138">
   <si>
     <t>analysis_id</t>
   </si>
@@ -482,13 +484,16 @@
   </si>
   <si>
     <t>interference_contribution</t>
+  </si>
+  <si>
+    <t>S1P d20:1 [M&gt;113]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -646,6 +651,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -989,7 +1000,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -998,6 +1009,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6999,6 +7011,910 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9557FE-D034-4647-A5F0-84D7A465854A}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4">
+        <v>3.1587200000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5">
+        <v>3.1538499999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12">
+        <v>2.8666500000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13">
+        <v>2.86123E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305DC38E-9D26-0B49-AA0F-CABFD88903E9}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5">
+        <v>3.1538499999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12">
+        <v>2.8666500000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13">
+        <v>2.86123E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J37" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4946AB-D291-A441-8BD4-AFE744BDE9E2}">
   <dimension ref="A1:K16"/>
